--- a/Тест2/267.xlsx
+++ b/Тест2/267.xlsx
@@ -105,19 +105,19 @@
     <t xml:space="preserve">Sutga ishlab chiqarishda tushishi mumkin bo'lgan patogenlar qaysilar?</t>
   </si>
   <si>
-    <t xml:space="preserve">Treponema va Borrelia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rikketsiya va xlamidiya</t>
+    <t xml:space="preserve">Treponema va Borrelia turlari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rikketsiyalar va xlamidiyalar</t>
   </si>
   <si>
     <t xml:space="preserve">Salmonellalar va stafilokokklar</t>
   </si>
   <si>
-    <t xml:space="preserve">Mikoplazma va ureaplazma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gonokokk va meningokokk</t>
+    <t xml:space="preserve">Mikoplazma va ureaplazmalar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gonokokk va meningokokklar</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Salmonellalar va stafilokokklar. Salmonellalar va stafilokokklar sutga ishlab chiqarish yoki saqlash davrida tushishi mumkin. Manba: Mavzu materiali (267.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019).</t>
